--- a/data/raw/data_articles/datajournal_articles git V final_3.xlsx
+++ b/data/raw/data_articles/datajournal_articles git V final_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bliv10\Desktop\DCC github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bliv10\Desktop\Github Data Articles Blanka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15112E2-1FB8-4FE8-A598-F07C2770C172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5550838D-B807-45C4-9C1D-A31750503887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datasets_reuses" sheetId="2" r:id="rId1"/>
@@ -25,11 +25,14 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -101,21 +104,12 @@
     <t>https://doi.org/10.17605/OSF.IO/8MBRU</t>
   </si>
   <si>
-    <t>Article Number</t>
-  </si>
-  <si>
     <t>Reusing article number</t>
   </si>
   <si>
-    <t>DOIs/links of articles that reused data</t>
-  </si>
-  <si>
     <t>Dataset cited</t>
   </si>
   <si>
-    <t>year of citing article</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1038/s41467-023-39916-1</t>
   </si>
   <si>
@@ -456,6 +450,15 @@
   </si>
   <si>
     <t>https://doi.org/10.21203/rs.3.rs-3976380/v1</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>DOI/link of article that reused data</t>
+  </si>
+  <si>
+    <t>Year of reusing article</t>
   </si>
 </sst>
 </file>
@@ -1065,9 +1068,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1105,7 +1108,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1211,7 +1214,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1353,7 +1356,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1362,35 +1365,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" customWidth="1"/>
-    <col min="4" max="5" width="46.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" customWidth="1"/>
+    <col min="4" max="5" width="46.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="F1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>7</v>
       </c>
@@ -1401,16 +1404,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>7</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>11</v>
@@ -1430,7 +1433,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>7</v>
       </c>
@@ -1441,16 +1444,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
@@ -1461,16 +1464,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>7</v>
       </c>
@@ -1481,16 +1484,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>11</v>
@@ -1510,7 +1513,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1521,16 +1524,16 @@
         <v>8</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>2023</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1541,16 +1544,16 @@
         <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>2023</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1561,16 +1564,16 @@
         <v>9</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <v>2022</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>12</v>
@@ -1590,7 +1593,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1601,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
@@ -1610,7 +1613,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -1630,7 +1633,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>9</v>
       </c>
@@ -1641,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
@@ -1650,7 +1653,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>9</v>
       </c>
@@ -1661,7 +1664,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -1670,7 +1673,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>9</v>
       </c>
@@ -1681,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
@@ -1690,7 +1693,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>9</v>
       </c>
@@ -1701,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
@@ -1710,7 +1713,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>9</v>
       </c>
@@ -1721,7 +1724,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>13</v>
@@ -1730,7 +1733,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>9</v>
       </c>
@@ -1741,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
@@ -1750,7 +1753,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1761,7 +1764,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
@@ -1770,7 +1773,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -1790,7 +1793,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>9</v>
       </c>
@@ -1801,7 +1804,7 @@
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -1810,7 +1813,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>9</v>
       </c>
@@ -1821,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -1830,7 +1833,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>9</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
@@ -1850,7 +1853,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>9</v>
       </c>
@@ -1861,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -1870,7 +1873,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>9</v>
       </c>
@@ -1881,7 +1884,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
@@ -1890,7 +1893,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>9</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>16</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>13</v>
@@ -1910,7 +1913,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>9</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>17</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>13</v>
@@ -1930,7 +1933,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>9</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>13</v>
@@ -1950,7 +1953,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>9</v>
       </c>
@@ -1961,7 +1964,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>13</v>
@@ -1970,7 +1973,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>9</v>
       </c>
@@ -1981,7 +1984,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>13</v>
@@ -1990,7 +1993,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>9</v>
       </c>
@@ -2001,7 +2004,7 @@
         <v>21</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>13</v>
@@ -2010,7 +2013,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>9</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>13</v>
@@ -2030,7 +2033,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9</v>
       </c>
@@ -2041,7 +2044,7 @@
         <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>13</v>
@@ -2050,7 +2053,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>9</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>13</v>
@@ -2070,7 +2073,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>9</v>
       </c>
@@ -2081,7 +2084,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
@@ -2090,7 +2093,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>9</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>26</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
@@ -2110,7 +2113,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>9</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>27</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>13</v>
@@ -2130,7 +2133,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>9</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>13</v>
@@ -2150,7 +2153,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>11</v>
       </c>
@@ -2161,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>14</v>
@@ -2170,7 +2173,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>11</v>
       </c>
@@ -2181,7 +2184,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>14</v>
@@ -2190,7 +2193,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>11</v>
       </c>
@@ -2201,7 +2204,7 @@
         <v>3</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>14</v>
@@ -2210,7 +2213,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>11</v>
       </c>
@@ -2221,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>14</v>
@@ -2230,7 +2233,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14</v>
       </c>
@@ -2241,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>15</v>
@@ -2250,7 +2253,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14</v>
       </c>
@@ -2261,7 +2264,7 @@
         <v>2</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>15</v>
@@ -2270,7 +2273,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14</v>
       </c>
@@ -2281,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>15</v>
@@ -2290,7 +2293,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14</v>
       </c>
@@ -2301,7 +2304,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>15</v>
@@ -2310,7 +2313,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14</v>
       </c>
@@ -2321,16 +2324,16 @@
         <v>5</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F48">
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>14</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>15</v>
@@ -2350,7 +2353,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>14</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>15</v>
@@ -2370,7 +2373,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>14</v>
       </c>
@@ -2381,7 +2384,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>15</v>
@@ -2390,7 +2393,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>14</v>
       </c>
@@ -2401,7 +2404,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>15</v>
@@ -2410,7 +2413,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>14</v>
       </c>
@@ -2421,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>15</v>
@@ -2430,7 +2433,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>14</v>
       </c>
@@ -2441,7 +2444,7 @@
         <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>15</v>
@@ -2450,7 +2453,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>14</v>
       </c>
@@ -2461,7 +2464,7 @@
         <v>12</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>15</v>
@@ -2470,7 +2473,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>14</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>15</v>
@@ -2490,7 +2493,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>14</v>
       </c>
@@ -2501,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>15</v>
@@ -2510,7 +2513,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>14</v>
       </c>
@@ -2521,7 +2524,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>15</v>
@@ -2530,7 +2533,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>14</v>
       </c>
@@ -2541,7 +2544,7 @@
         <v>16</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>15</v>
@@ -2550,7 +2553,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>14</v>
       </c>
@@ -2561,7 +2564,7 @@
         <v>17</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>15</v>
@@ -2570,7 +2573,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>14</v>
       </c>
@@ -2581,7 +2584,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>15</v>
@@ -2590,7 +2593,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>14</v>
       </c>
@@ -2601,7 +2604,7 @@
         <v>19</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>15</v>
@@ -2610,7 +2613,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>14</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>20</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>15</v>
@@ -2630,7 +2633,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>14</v>
       </c>
@@ -2641,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>15</v>
@@ -2650,7 +2653,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>14</v>
       </c>
@@ -2661,7 +2664,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>15</v>
@@ -2670,7 +2673,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>14</v>
       </c>
@@ -2681,7 +2684,7 @@
         <v>23</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>15</v>
@@ -2690,7 +2693,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>14</v>
       </c>
@@ -2701,7 +2704,7 @@
         <v>24</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>15</v>
@@ -2710,7 +2713,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>14</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>15</v>
@@ -2730,7 +2733,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>14</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>26</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>15</v>
@@ -2750,7 +2753,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>14</v>
       </c>
@@ -2761,7 +2764,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>15</v>
@@ -2770,7 +2773,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>14</v>
       </c>
@@ -2781,7 +2784,7 @@
         <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>15</v>
@@ -2790,7 +2793,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>14</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>29</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>15</v>
@@ -2810,7 +2813,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>14</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>30</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>15</v>
@@ -2830,7 +2833,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>14</v>
       </c>
@@ -2841,7 +2844,7 @@
         <v>31</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>15</v>
@@ -2850,7 +2853,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>14</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>32</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>15</v>
@@ -2870,7 +2873,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>14</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>33</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>15</v>
@@ -2890,7 +2893,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14</v>
       </c>
@@ -2901,7 +2904,7 @@
         <v>34</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>15</v>
@@ -2910,7 +2913,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14</v>
       </c>
@@ -2921,7 +2924,7 @@
         <v>35</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>15</v>
@@ -2930,7 +2933,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14</v>
       </c>
@@ -2941,16 +2944,16 @@
         <v>36</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F79">
         <v>2024</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>14</v>
       </c>
@@ -2961,7 +2964,7 @@
         <v>37</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>15</v>
@@ -2970,7 +2973,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>14</v>
       </c>
@@ -2981,7 +2984,7 @@
         <v>38</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>15</v>
@@ -2990,7 +2993,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>14</v>
       </c>
@@ -3001,7 +3004,7 @@
         <v>39</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>15</v>
@@ -3010,7 +3013,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>14</v>
       </c>
@@ -3021,7 +3024,7 @@
         <v>40</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>15</v>
@@ -3030,7 +3033,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>16</v>
       </c>
@@ -3041,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
@@ -3050,7 +3053,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>23</v>
       </c>
@@ -3061,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>17</v>
@@ -3070,7 +3073,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>23</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>17</v>
@@ -3090,7 +3093,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>23</v>
       </c>
@@ -3101,7 +3104,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>17</v>
@@ -3110,7 +3113,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>23</v>
       </c>
@@ -3121,7 +3124,7 @@
         <v>4</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>17</v>
@@ -3130,7 +3133,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>24</v>
       </c>
@@ -3141,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>18</v>
@@ -3150,7 +3153,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>24</v>
       </c>
@@ -3161,7 +3164,7 @@
         <v>2</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>18</v>
@@ -3170,7 +3173,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>24</v>
       </c>
@@ -3181,7 +3184,7 @@
         <v>3</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>18</v>
@@ -3190,7 +3193,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>24</v>
       </c>
@@ -3201,7 +3204,7 @@
         <v>4</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>18</v>
@@ -3210,7 +3213,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>24</v>
       </c>
@@ -3221,7 +3224,7 @@
         <v>5</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>18</v>
@@ -3230,7 +3233,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>24</v>
       </c>
@@ -3241,7 +3244,7 @@
         <v>6</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>18</v>
@@ -3250,7 +3253,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>24</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>18</v>
@@ -3270,7 +3273,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>24</v>
       </c>
@@ -3281,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>18</v>
@@ -3290,7 +3293,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>24</v>
       </c>
@@ -3301,7 +3304,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>18</v>
@@ -3310,7 +3313,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>24</v>
       </c>
@@ -3321,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>18</v>
@@ -3330,7 +3333,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>24</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>11</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>18</v>
@@ -3350,7 +3353,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>24</v>
       </c>
@@ -3361,7 +3364,7 @@
         <v>12</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>18</v>
@@ -3370,7 +3373,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>24</v>
       </c>
@@ -3381,7 +3384,7 @@
         <v>13</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>18</v>
@@ -3390,7 +3393,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>24</v>
       </c>
@@ -3401,7 +3404,7 @@
         <v>14</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>18</v>
@@ -3410,7 +3413,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>24</v>
       </c>
@@ -3421,7 +3424,7 @@
         <v>15</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>18</v>
@@ -3430,7 +3433,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>24</v>
       </c>
@@ -3441,7 +3444,7 @@
         <v>16</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>18</v>
@@ -3450,7 +3453,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>24</v>
       </c>
@@ -3461,7 +3464,7 @@
         <v>17</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>18</v>
@@ -3470,7 +3473,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>24</v>
       </c>
@@ -3481,7 +3484,7 @@
         <v>18</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>18</v>
@@ -3490,7 +3493,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>24</v>
       </c>
@@ -3501,7 +3504,7 @@
         <v>19</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>18</v>
@@ -3510,7 +3513,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>24</v>
       </c>
@@ -3521,7 +3524,7 @@
         <v>20</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>18</v>
@@ -3530,7 +3533,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>24</v>
       </c>
@@ -3541,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>18</v>
@@ -3550,7 +3553,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>24</v>
       </c>
@@ -3561,7 +3564,7 @@
         <v>22</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>18</v>
@@ -3570,7 +3573,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>24</v>
       </c>
@@ -3581,7 +3584,7 @@
         <v>23</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>18</v>
@@ -3590,7 +3593,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>27</v>
       </c>
@@ -3601,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>19</v>
@@ -3610,7 +3613,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>27</v>
       </c>
@@ -3621,7 +3624,7 @@
         <v>2</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>14</v>
@@ -3630,7 +3633,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>28</v>
       </c>
@@ -3641,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>20</v>
@@ -3650,7 +3653,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
     </row>
@@ -3880,14 +3883,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a0e84d40-090a-490d-8a02-2942ffba970a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaacefca-f467-416c-abd0-2b181dff1e20">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4086,15 +4087,44 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a0e84d40-090a-490d-8a02-2942ffba970a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaacefca-f467-416c-abd0-2b181dff1e20">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647AA23E-A486-48B9-BA40-113933E28953}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5F17F50-E96C-4AA3-9082-9354A0940F1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
+    <ds:schemaRef ds:uri="a0e84d40-090a-490d-8a02-2942ffba970a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2D3F5D9-F66A-401E-BC58-4588B5177296}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4103,16 +4133,4 @@
     <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5F17F50-E96C-4AA3-9082-9354A0940F1E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647AA23E-A486-48B9-BA40-113933E28953}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>